--- a/results/walkforward/SPYG/wf_SPYG_1e-07_0.001_8_5.xlsx
+++ b/results/walkforward/SPYG/wf_SPYG_1e-07_0.001_8_5.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="50" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="100" uniqueCount="42">
   <si>
     <t>Ticker</t>
   </si>
@@ -378,7 +378,7 @@
         <v>-0.098848684736707604</v>
       </c>
       <c r="H2" s="0">
-        <v>-3.7280665610042174</v>
+        <v>-0.7094202103259617</v>
       </c>
       <c r="I2" s="0">
         <v>-20.600359082079432</v>
@@ -387,7 +387,7 @@
         <v>-20.600359082079432</v>
       </c>
       <c r="K2" s="0">
-        <v>-20.212874320140706</v>
+        <v>-20.60035908207951</v>
       </c>
       <c r="L2" s="0">
         <v>0.092488820828829602</v>
@@ -396,7 +396,7 @@
         <v>0.092488820828829602</v>
       </c>
       <c r="N2" s="0">
-        <v>-0.10975011964925063</v>
+        <v>0.060088777258979265</v>
       </c>
       <c r="O2" s="0">
         <v>1</v>
@@ -423,7 +423,7 @@
         <v>0</v>
       </c>
       <c r="W2" s="0">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="X2" s="0">
         <v>100</v>
@@ -435,16 +435,16 @@
         <v>100</v>
       </c>
       <c r="AA2" s="0">
-        <v>97.111553784860561</v>
+        <v>99.302788844621517</v>
       </c>
       <c r="AB2" s="0">
-        <v>3</v>
+        <v>0.94999999999999996</v>
       </c>
       <c r="AC2" s="0">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="AD2" s="0">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AE2" s="0">
         <v>0.875</v>
@@ -459,7 +459,7 @@
         <v>0</v>
       </c>
       <c r="AI2" s="0">
-        <v>-3.6292178762675098</v>
+        <v>-0.61057152558925409</v>
       </c>
       <c r="AJ2" s="0">
         <v>0</v>
@@ -468,7 +468,7 @@
         <v>0</v>
       </c>
       <c r="AL2" s="0">
-        <v>0.38748476193872783</v>
+        <v>-7.7715611723760958e-14</v>
       </c>
       <c r="AM2" s="0">
         <v>0</v>
@@ -477,7 +477,7 @@
         <v>0</v>
       </c>
       <c r="AO2" s="0">
-        <v>-0.20223894047808022</v>
+        <v>-0.032400043569850337</v>
       </c>
     </row>
     <row r="3">
@@ -503,7 +503,7 @@
         <v>30.833199910339747</v>
       </c>
       <c r="H3" s="0">
-        <v>32.602484796848465</v>
+        <v>31.717342793354895</v>
       </c>
       <c r="I3" s="0">
         <v>-6.356251525301893</v>
@@ -512,7 +512,7 @@
         <v>-6.356251525301893</v>
       </c>
       <c r="K3" s="0">
-        <v>-6.3562515253019143</v>
+        <v>-6.356251525301893</v>
       </c>
       <c r="L3" s="0">
         <v>2.1462149309842649</v>
@@ -521,7 +521,7 @@
         <v>2.1462149309842649</v>
       </c>
       <c r="N3" s="0">
-        <v>2.2821062064228377</v>
+        <v>2.2160282957334916</v>
       </c>
       <c r="O3" s="0">
         <v>1</v>
@@ -560,10 +560,10 @@
         <v>100</v>
       </c>
       <c r="AA3" s="0">
-        <v>99.801587301587304</v>
+        <v>99.900793650793645</v>
       </c>
       <c r="AB3" s="0">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="AC3" s="0">
         <v>0</v>
@@ -584,7 +584,7 @@
         <v>0</v>
       </c>
       <c r="AI3" s="0">
-        <v>1.7692848865087152</v>
+        <v>0.88414288301514876</v>
       </c>
       <c r="AJ3" s="0">
         <v>0</v>
@@ -593,7 +593,7 @@
         <v>0</v>
       </c>
       <c r="AL3" s="0">
-        <v>-2.2204460492503131e-14</v>
+        <v>0</v>
       </c>
       <c r="AM3" s="0">
         <v>0</v>
@@ -602,7 +602,7 @@
         <v>0</v>
       </c>
       <c r="AO3" s="0">
-        <v>0.13589127543857282</v>
+        <v>0.069813364749226725</v>
       </c>
     </row>
     <row r="4">
@@ -628,7 +628,7 @@
         <v>48.632508085214752</v>
       </c>
       <c r="H4" s="0">
-        <v>51.460572366482204</v>
+        <v>50.182078601657423</v>
       </c>
       <c r="I4" s="0">
         <v>-31.269528703541372</v>
@@ -637,7 +637,7 @@
         <v>-13.971557711939898</v>
       </c>
       <c r="K4" s="0">
-        <v>-12.700893998527862</v>
+        <v>-13.759040270453138</v>
       </c>
       <c r="L4" s="0">
         <v>1.0040977502243584</v>
@@ -646,7 +646,7 @@
         <v>1.8435008179765755</v>
       </c>
       <c r="N4" s="0">
-        <v>1.9864130059745821</v>
+        <v>1.8957196279108226</v>
       </c>
       <c r="O4" s="0">
         <v>1</v>
@@ -673,7 +673,7 @@
         <v>4</v>
       </c>
       <c r="W4" s="0">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="X4" s="0">
         <v>100</v>
@@ -685,16 +685,16 @@
         <v>88.932806324110672</v>
       </c>
       <c r="AA4" s="0">
-        <v>87.351778656126484</v>
+        <v>88.656126482213452</v>
       </c>
       <c r="AB4" s="0">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="AC4" s="0">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AD4" s="0">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AE4" s="0">
         <v>1</v>
@@ -709,7 +709,7 @@
         <v>15.170680629569745</v>
       </c>
       <c r="AI4" s="0">
-        <v>17.998744910837196</v>
+        <v>16.720251146012409</v>
       </c>
       <c r="AJ4" s="0">
         <v>0</v>
@@ -718,7 +718,7 @@
         <v>17.297970991601474</v>
       </c>
       <c r="AL4" s="0">
-        <v>18.568634705013508</v>
+        <v>17.510488433088234</v>
       </c>
       <c r="AM4" s="0">
         <v>0</v>
@@ -727,7 +727,7 @@
         <v>0.83940306775221707</v>
       </c>
       <c r="AO4" s="0">
-        <v>0.98231525575022371</v>
+        <v>0.89162187768646417</v>
       </c>
     </row>
     <row r="5">
@@ -878,7 +878,7 @@
         <v>-24.245971376067644</v>
       </c>
       <c r="H6" s="0">
-        <v>-24.460275298666957</v>
+        <v>-24.095693114109839</v>
       </c>
       <c r="I6" s="0">
         <v>-32.261519608180947</v>
@@ -887,7 +887,7 @@
         <v>-29.962933741616837</v>
       </c>
       <c r="K6" s="0">
-        <v>-28.855913190357953</v>
+        <v>-29.439494765232233</v>
       </c>
       <c r="L6" s="0">
         <v>-0.99513231032002081</v>
@@ -896,7 +896,7 @@
         <v>-1.0285799861772555</v>
       </c>
       <c r="N6" s="0">
-        <v>-1.0763324862253341</v>
+        <v>-1.0348779547064719</v>
       </c>
       <c r="O6" s="0">
         <v>1</v>
@@ -935,10 +935,10 @@
         <v>72.509960159362549</v>
       </c>
       <c r="AA6" s="0">
-        <v>69.721115537848604</v>
+        <v>71.75298804780877</v>
       </c>
       <c r="AB6" s="0">
-        <v>7</v>
+        <v>6.5</v>
       </c>
       <c r="AC6" s="0">
         <v>15</v>
@@ -959,7 +959,7 @@
         <v>5.3668086204595173</v>
       </c>
       <c r="AI6" s="0">
-        <v>5.1525046978602056</v>
+        <v>5.5170868824173214</v>
       </c>
       <c r="AJ6" s="0">
         <v>0</v>
@@ -968,7 +968,7 @@
         <v>2.2985858665641068</v>
       </c>
       <c r="AL6" s="0">
-        <v>3.4056064178229928</v>
+        <v>2.8220248429487116</v>
       </c>
       <c r="AM6" s="0">
         <v>0</v>
@@ -977,7 +977,7 @@
         <v>-0.033447675857234738</v>
       </c>
       <c r="AO6" s="0">
-        <v>-0.081200175905313254</v>
+        <v>-0.039745644386451118</v>
       </c>
     </row>
     <row r="7">
@@ -1128,7 +1128,7 @@
         <v>35.106055948355184</v>
       </c>
       <c r="H8" s="0">
-        <v>35.521515738591972</v>
+        <v>35.106055948355184</v>
       </c>
       <c r="I8" s="0">
         <v>-12.746730083234258</v>
@@ -1137,7 +1137,7 @@
         <v>-12.746730083234258</v>
       </c>
       <c r="K8" s="0">
-        <v>-12.478420680205382</v>
+        <v>-12.746730083234258</v>
       </c>
       <c r="L8" s="0">
         <v>1.7924158170424755</v>
@@ -1146,7 +1146,7 @@
         <v>1.7924158170424755</v>
       </c>
       <c r="N8" s="0">
-        <v>1.8275256756097</v>
+        <v>1.7924158170424755</v>
       </c>
       <c r="O8" s="0">
         <v>1</v>
@@ -1173,7 +1173,7 @@
         <v>0</v>
       </c>
       <c r="W8" s="0">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="X8" s="0">
         <v>100</v>
@@ -1185,16 +1185,16 @@
         <v>100</v>
       </c>
       <c r="AA8" s="0">
-        <v>99.702380952380949</v>
+        <v>100</v>
       </c>
       <c r="AB8" s="0">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="AC8" s="0">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AD8" s="0">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AE8" s="0">
         <v>0.5</v>
@@ -1209,7 +1209,7 @@
         <v>0</v>
       </c>
       <c r="AI8" s="0">
-        <v>0.41545979023678292</v>
+        <v>0</v>
       </c>
       <c r="AJ8" s="0">
         <v>0</v>
@@ -1218,7 +1218,7 @@
         <v>0</v>
       </c>
       <c r="AL8" s="0">
-        <v>0.26830940302887685</v>
+        <v>0</v>
       </c>
       <c r="AM8" s="0">
         <v>0</v>
@@ -1227,7 +1227,7 @@
         <v>0</v>
       </c>
       <c r="AO8" s="0">
-        <v>0.035109858567224483</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -1253,7 +1253,7 @@
         <v>17.931825365073738</v>
       </c>
       <c r="H9" s="0">
-        <v>20.895372796997979</v>
+        <v>19.03821516022861</v>
       </c>
       <c r="I9" s="0">
         <v>-22.253490637514915</v>
@@ -1262,7 +1262,7 @@
         <v>-24.467062368040249</v>
       </c>
       <c r="K9" s="0">
-        <v>-22.836060242203594</v>
+        <v>-23.758442187394703</v>
       </c>
       <c r="L9" s="0">
         <v>0.95343034850768338</v>
@@ -1271,7 +1271,7 @@
         <v>0.84401371670864311</v>
       </c>
       <c r="N9" s="0">
-        <v>0.97246256464239911</v>
+        <v>0.88974890626525172</v>
       </c>
       <c r="O9" s="0">
         <v>1</v>
@@ -1298,7 +1298,7 @@
         <v>2</v>
       </c>
       <c r="W9" s="0">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="X9" s="0">
         <v>100</v>
@@ -1310,16 +1310,16 @@
         <v>95.199999999999989</v>
       </c>
       <c r="AA9" s="0">
-        <v>94.199999999999989</v>
+        <v>95.060000000000002</v>
       </c>
       <c r="AB9" s="0">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="AC9" s="0">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AD9" s="0">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AE9" s="0">
         <v>1</v>
@@ -1334,7 +1334,7 @@
         <v>-3.4561154767921876</v>
       </c>
       <c r="AI9" s="0">
-        <v>-0.49256804486794703</v>
+        <v>-2.3497256816373158</v>
       </c>
       <c r="AJ9" s="0">
         <v>0</v>
@@ -1343,7 +1343,7 @@
         <v>-2.2135717305253322</v>
       </c>
       <c r="AL9" s="0">
-        <v>-0.58256960468867636</v>
+        <v>-1.504951549879785</v>
       </c>
       <c r="AM9" s="0">
         <v>0</v>
@@ -1352,7 +1352,7 @@
         <v>-0.10941663179904026</v>
       </c>
       <c r="AO9" s="0">
-        <v>0.019032216134715729</v>
+        <v>-0.063681442242431663</v>
       </c>
     </row>
     <row r="10">
